--- a/tests/worked_examples/subsidies/combined_rate_cap_pro_rata.xlsx
+++ b/tests/worked_examples/subsidies/combined_rate_cap_pro_rata.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc"/>
+  <fileVersion appName="Calc" lowestEdited="4"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
@@ -24,6 +24,8 @@
     <definedName function="false" hidden="false" name="scheme_b_benefit_kind" vbProcedure="false">Example!$B$18</definedName>
     <definedName function="false" hidden="false" name="scheme_b_payout_kind" vbProcedure="false">Example!$B$19</definedName>
     <definedName function="false" hidden="false" name="scheme_b_rate" vbProcedure="false">Example!$B$20</definedName>
+    <definedName function="false" hidden="false" name="support_ledger_npv_in_euro" vbProcedure="false">Example!$B$28</definedName>
+    <definedName function="false" hidden="false" name="support_npv_in_euro" vbProcedure="false">Example!$B$27</definedName>
     <definedName function="false" hidden="false" name="total_upfront_award_in_euro" vbProcedure="false">Example!$B$25</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="52">
   <si>
     <t xml:space="preserve">METADATA</t>
   </si>
@@ -65,7 +67,7 @@
     <t xml:space="preserve">description</t>
   </si>
   <si>
-    <t xml:space="preserve">Two share-based schemes in one cumulation group ask for 30 % and 20 %, but the group's combined rate is capped at 40 %. Both rates are scaled down pro rata by the same factor 0.40/0.50, so each scheme keeps its relative weight and the sum hits the cap exactly.</t>
+    <t xml:space="preserve">Two share-based schemes in one cumulation group ask for 30 % and 20 % of the same 20,000 EUR measure cost, but the group's combined rate is capped at 40 %. Both rates are scaled down pro rata by the same factor 0.40/0.50, so each scheme keeps its relative weight and the sum hits the cap exactly.</t>
   </si>
   <si>
     <t xml:space="preserve">reviewed_by</t>
@@ -95,7 +97,7 @@
     <t xml:space="preserve">interest_rate</t>
   </si>
   <si>
-    <t xml:space="preserve">discount rate of the solver objective</t>
+    <t xml:space="preserve">the runner's solver objective requires a discount rate; it has no effect here, both awards being upfront grants at year 0</t>
   </si>
   <si>
     <t xml:space="preserve">cumulation_group</t>
@@ -161,7 +163,7 @@
     <t xml:space="preserve">note</t>
   </si>
   <si>
-    <t xml:space="preserve">sign convention: cost positive, revenue / subsidy / residual value negative</t>
+    <t xml:space="preserve">sign convention: solver quantities are award magnitudes (positive); they enter the ledger as negative cost via as_revenue() (§3.9)</t>
   </si>
   <si>
     <t xml:space="preserve">scheme_a_award_in_euro</t>
@@ -180,6 +182,18 @@
   </si>
   <si>
     <t xml:space="preserve">equals the combined rate cap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">support_npv_in_euro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">both awards are upfront grants paid at year 0, so the support NPV is their sum, undiscounted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">support_ledger_npv_in_euro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the same support as it lands on the ledger: negative cost (§3.9)</t>
   </si>
 </sst>
 </file>
@@ -262,12 +276,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -471,276 +489,306 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="C1" s="3"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="C2" s="3"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="C3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="2"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="C4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="2"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="2"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="2"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C9" s="2"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11" s="1" t="n">
         <v>20000</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="0" t="n">
+      <c r="B12" s="1" t="n">
         <v>0.03</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14" s="1" t="n">
         <v>0.4</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="0" t="n">
+      <c r="B17" s="1" t="n">
         <v>0.3</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="0" t="n">
+      <c r="B20" s="1" t="n">
         <v>0.2</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C21" s="2"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C21" s="3"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="0" t="s">
+      <c r="E22" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B23" s="0" t="n">
+      <c r="B23" s="1" t="n">
         <f aca="false">measure_cost_in_euro*scheme_a_rate*combined_rate_cap/(scheme_a_rate+scheme_b_rate)</f>
         <v>4800</v>
       </c>
-      <c r="C23" s="2" t="n">
+      <c r="C23" s="3" t="n">
         <v>0.01</v>
       </c>
-      <c r="D23" s="0" t="s">
+      <c r="D23" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="0" t="n">
+      <c r="B24" s="1" t="n">
         <f aca="false">measure_cost_in_euro*scheme_b_rate*combined_rate_cap/(scheme_a_rate+scheme_b_rate)</f>
         <v>3200</v>
       </c>
-      <c r="C24" s="2" t="n">
+      <c r="C24" s="3" t="n">
         <v>0.01</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B25" s="0" t="n">
+      <c r="B25" s="1" t="n">
         <f aca="false">scheme_a_award_in_euro+scheme_b_award_in_euro</f>
         <v>8000</v>
       </c>
-      <c r="C25" s="2" t="n">
+      <c r="C25" s="3" t="n">
         <v>0.01</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B26" s="0" t="n">
+      <c r="B26" s="1" t="n">
         <f aca="false">total_upfront_award_in_euro/measure_cost_in_euro</f>
         <v>0.4</v>
       </c>
-      <c r="C26" s="2" t="n">
+      <c r="C26" s="3" t="n">
         <v>1E-006</v>
       </c>
-      <c r="D26" s="0" t="s">
+      <c r="D26" s="1" t="s">
         <v>47</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B27" s="1" t="n">
+        <f aca="false">total_upfront_award_in_euro</f>
+        <v>8000</v>
+      </c>
+      <c r="C27" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B28" s="1" t="n">
+        <f aca="false">-support_npv_in_euro</f>
+        <v>-8000</v>
+      </c>
+      <c r="C28" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
